--- a/www/download/COUNTRY.IND.zdW16.xlsx
+++ b/www/download/COUNTRY.IND.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Índia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>44.9068859082038</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>47.1820517847237</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>48.626306401802</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>46.5646898431443</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>45.3048331873266</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>44.086268137754</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>45.2935477010772</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>41.2738764817925</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>43.239316471179</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>48.36876397147</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>45.7124047403807</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>46.5265601586914</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>53.3469907824012</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>58.347482904674</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61.0128130274123</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>410.063</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>420.903</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>432.113</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>444.312</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>457.919</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>460.24</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>459.57</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>459.864</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>460.178</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>461.62</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>466.169</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>473.775</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>540.263</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>609.186</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>658.776</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>193.583</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>194.762</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>195.964</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>197.756</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>200.489</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>204.577</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>209.874</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>215.987</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>221.965</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>228.908</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>229.699</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>230.251</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>259.218</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>290.083</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>314.882</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>946052.946</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>973681.83</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1002443.878</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1033812.503</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1068802.725</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1077779.934</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1077119.508</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1078735.397</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1080383.099</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1084735.105</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1096986.716</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1116767.369</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1274604.663</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1438109.826</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1557808.828</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>445332.627</t>
+          <t>1161523881875.92</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>449907.673</t>
+          <t>1193268967845.55</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>454652.7</t>
+          <t>1236423340057.57</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>460906.026</t>
+          <t>1304949981034.73</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>469523.859</t>
+          <t>1346618294856.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>481211.636</t>
+          <t>1336297857442.95</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>493947.562</t>
+          <t>1328622117333.09</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>508653.299</t>
+          <t>1323079997077.16</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>523074.027</t>
+          <t>1310348795910.59</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>539838.332</t>
+          <t>1316024453442.07</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>542896.428</t>
+          <t>1329283859063.01</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>545686.993</t>
+          <t>1345681449875.16</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>614660.341</t>
+          <t>1486477257617.2</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>688095.379</t>
+          <t>1630788870922.18</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>747929.795</t>
+          <t>1737602577361.21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>180723894687.524</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>178777896974.411</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>178621832550.175</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>179399936316.026</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>177238967022.934</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>179382310179.335</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>177743881235.775</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>180960663434.701</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>178732095721.187</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>182254931702.034</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>179070902784.296</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>183264378130.96</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>198055985326.678</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>216570583804.988</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>230929680935.897</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>38659022.2169429</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>38959486.6805943</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>39777137.3398066</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>35472355.6654053</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>32793114.895922</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>28334965.3181259</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>24698276.0374931</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>19335362.4300968</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>17535465.0033955</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>17207323.2052627</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>13822055.2691951</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>12421366.7956707</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>14252980.4394104</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>15321698.5267926</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>15921262.5359048</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6889038.32236492</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6964244.1391554</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7206398.21819677</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8067265.70943234</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>9148654.3652937</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>9919465.49111821</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>10431620.8738331</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>11668729.7902376</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>12721100.0150265</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>11646611.8249482</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>12932349.5034747</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>13910500.3932749</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>15418153.2664806</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>17095653.6151437</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>18288157.3876224</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10536577.8057969</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10666047.4179846</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>11133077.0713025</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>12792348.4957707</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>14547573.2167109</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>15592170.9314339</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>16381790.6498283</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>18299916.0154315</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>19766968.2407899</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>18143192.2596062</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>20247043.6907474</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>21854162.4705849</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>23581014.9399993</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>25720324.4806596</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>27500630.6795774</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.46416019182185</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.51657324878588</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.54533666746637</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.56915378826044</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.64910062886592</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.68260362751999</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.7789848998784</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.81085010048908</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.92658140044398</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.96199574386592</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.03174005133574</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.97759443796576</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.10346763813356</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.17723380022653</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.23877724149117</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>44.9068859082038</t>
+          <t>933.572281193204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>47.1820517847237</t>
+          <t>917.931708940725</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>48.626306401802</t>
+          <t>911.505020345742</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>46.5646898431443</t>
+          <t>907.179987359783</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>45.3048331873266</t>
+          <t>884.03423334751</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>44.086268137754</t>
+          <t>876.843899733281</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>45.2935477010772</t>
+          <t>846.905831715936</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>41.2738764817925</t>
+          <t>837.832628066913</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>43.239316471179</t>
+          <t>805.227833537581</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>48.36876397147</t>
+          <t>796.191857334608</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>45.7124047403807</t>
+          <t>779.58846123251</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>46.5265601586914</t>
+          <t>795.93173219124</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>53.3469907824012</t>
+          <t>764.052008201414</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>58.347482904674</t>
+          <t>746.581223622774</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>61.0128130274123</t>
+          <t>733.384847455111</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>-53916796851.7867</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>-55230916627.8752</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>-62614474571.618</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>-57561728820.7658</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>-64345861160.6844</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-60135918365.9373</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>-63277234138.8053</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-49013392341.1177</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>-47059713438.374</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>-39848737313.8718</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>-39316347380.7842</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>-42394909528.4007</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>-63005960903.8965</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>-83859311060.445</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>-78351539142.3997</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>-54467899870.0846</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-55871351654.9769</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>-63314114774.4669</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>-58742379270.0809</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>-65972278035.3079</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>-62336729342.2642</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>-66812701365.2605</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-53841596335.3583</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>-52174651397.3441</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>-44151232952.9682</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-45218572725.3511</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>-49302997251.1393</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>-69145617731.9825</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>-89344836213.4252</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-83757029638.1428</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>551103018.297888</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.315</t>
+          <t>640435027.101748</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.377</t>
+          <t>699640202.848938</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>1180650449.31505</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.927</t>
+          <t>1626416874.62354</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2200810976.32691</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.482</t>
+          <t>3535467226.45523</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.171</t>
+          <t>4828203994.24066</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>5114937958.97005</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.603</t>
+          <t>4302495639.09635</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>4.413</t>
+          <t>5902225344.56688</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>5.075</t>
+          <t>6908087722.73865</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>5.347</t>
+          <t>6139656828.08595</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5485525152.98018</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6.166</t>
+          <t>5405490495.74313</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>2300.47165150461</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>2310.04238293254</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>2320.0871508657</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>2330.68490115944</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.383</t>
+          <t>2341.89564349989</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.609</t>
+          <t>2352.22462619328</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>2353.53851795754</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.352</t>
+          <t>2355.02192679491</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.589</t>
+          <t>2356.56480075089</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.636</t>
+          <t>2358.31689272581</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.338</t>
+          <t>2363.5095614778</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.866</t>
+          <t>2369.96189877309</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2371.21068130405</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.781</t>
+          <t>2372.06309830876</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.984</t>
+          <t>2375.27015319209</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>2307.08920623806</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>2313.31711731959</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>2319.86359421294</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>2326.77027791454</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>2334.04135843191</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>2341.77719478986</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>2343.75423298402</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>2345.77038000747</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>2347.74892428654</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>2349.84188329448</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>2353.19378580915</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.844</t>
+          <t>2357.16911572013</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.823</t>
+          <t>2359.22835711245</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>2360.70535628087</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.994</t>
+          <t>2364.70132143668</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>62050.1726381485</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>62398.7438409319</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>73967.4686181423</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>86559.1747565847</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>120708.19811972</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>156366.063778266</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>197504.414090529</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>236114.360973164</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>252446.125362487</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>222557.561788275</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>315327.852985222</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>360916.825092154</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>357325.34940172</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>380886.436094993</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>369456.459605055</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>64295915820.489</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>66212726437.5554</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>75460765811.5226</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>71921454783.9185</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>81127043702.9244</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>79847060419.1789</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>81767582298.0159</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>69779771128.6487</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>66232568101.2054</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>61020736258.9517</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>65893290108.6131</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>72170872943.7275</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>92892228675.0302</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>115430189704.987</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>110037815610.707</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>67101.9950733477</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>67004.1171447722</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>77660.4615919084</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>91654.5898946378</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>135032.09869782</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>181296.135484551</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>225282.178015036</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>275085.904266317</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>297933.092386165</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>272287.257918997</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>363222.77086478</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>414015.954229131</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>411275.45981507</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>386312.502923851</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>372206.706569102</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>946052.946</t>
+          <t>11069980388.9601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>973681.83</t>
+          <t>11637296620.7513</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1002443.878</t>
+          <t>13375233222.4978</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1033812.503</t>
+          <t>15047656772.6985</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1068802.725</t>
+          <t>18543363766.1937</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1077779.934</t>
+          <t>22492818719.3853</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1077119.508</t>
+          <t>21303231218.2971</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1078735.397</t>
+          <t>24150333943.2165</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1080383.099</t>
+          <t>22621167077.7341</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1084735.105</t>
+          <t>25406567656.4501</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1096986.716</t>
+          <t>30212526390.9893</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1116767.369</t>
+          <t>33591707964.9773</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1274604.663</t>
+          <t>33788991330.4683</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1438109.826</t>
+          <t>31967311187.7568</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1557808.828</t>
+          <t>31885281779.1171</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>445332.627</t>
+          <t>-5051.82243519918</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>449907.673</t>
+          <t>-4605.37330384031</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>454652.7</t>
+          <t>-3692.99297376613</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>460906.026</t>
+          <t>-5095.41513805307</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>469523.859</t>
+          <t>-14323.9005781001</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>481211.636</t>
+          <t>-24930.0717062846</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>493947.562</t>
+          <t>-27777.7639245067</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>508653.299</t>
+          <t>-38971.5432931526</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>523074.027</t>
+          <t>-45486.9670236784</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>539838.332</t>
+          <t>-49729.6961307225</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>542896.428</t>
+          <t>-47894.9178795583</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>545686.993</t>
+          <t>-53099.1291369773</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>614660.341</t>
+          <t>-53950.11041335</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>688095.379</t>
+          <t>-5426.0668288576</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>747929.795</t>
+          <t>-2750.24696404661</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1249024.231</t>
+          <t>53225935431.529</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1279284.897</t>
+          <t>54575429816.8041</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1319770.406</t>
+          <t>62085532589.0248</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1396292.597</t>
+          <t>56873798011.22</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1435081.517</t>
+          <t>62583679936.7306</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1420297.732</t>
+          <t>57354241699.7935</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1410996.457</t>
+          <t>60464351079.7188</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1413235.59</t>
+          <t>45629437185.4322</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1400121.588</t>
+          <t>43611401023.4713</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1415091.274</t>
+          <t>35614168602.5016</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1429135.544</t>
+          <t>35680763717.6238</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1449690.345</t>
+          <t>38579164978.7501</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1615118.585</t>
+          <t>59103237344.5619</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1769913.439</t>
+          <t>83462878517.2299</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1737602.577</t>
+          <t>78152533831.5898</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>10.148</t>
+          <t>268649.29935051</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10.295</t>
+          <t>272792.432882265</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>10.685</t>
+          <t>281705.219329225</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12.303</t>
+          <t>330308.671117189</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>386011.174119445</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>14.856</t>
+          <t>451636.766669136</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>15.593</t>
+          <t>511787.019346209</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>17.631</t>
+          <t>649638.185512618</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>701832.943797986</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>716628.202440659</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>19.511</t>
+          <t>896707.059879645</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>21.017</t>
+          <t>1013123.01064797</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>22.816</t>
+          <t>987568.072577642</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>1002565.27581638</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>27.501</t>
+          <t>1033797.92482284</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>759428.98</t>
+          <t>0.175692536396759</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>779128.021</t>
+          <t>0.177624762013392</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>800332.1</t>
+          <t>0.181043543041735</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>822943.359</t>
+          <t>0.182444748958463</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>846859.14</t>
+          <t>0.17509362083399</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>850129.244</t>
+          <t>0.182515739583144</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>846041.957</t>
+          <t>0.188832890919026</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>843646.657</t>
+          <t>0.187750386550479</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>843279.449</t>
+          <t>0.178848054421003</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>844792.126</t>
+          <t>0.178027856757492</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>849050.544</t>
+          <t>0.183326575208318</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>856546.315</t>
+          <t>0.180997268934556</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>971914.663</t>
+          <t>0.170268176569108</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1083944.399</t>
+          <t>0.166482881284847</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1155520.751</t>
+          <t>0.162845457043841</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>101917.222659708</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>102234.588629987</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6.479</t>
+          <t>104510.025359112</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>7.251</t>
+          <t>115724.172628345</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>127502.864829729</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>8.892</t>
+          <t>149617.068269718</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>9.349</t>
+          <t>170606.630167237</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>10.525</t>
+          <t>220152.667377834</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>11.419</t>
+          <t>244960.764328012</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>10.411</t>
+          <t>256552.916381948</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>11.592</t>
+          <t>321233.782375547</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>12.418</t>
+          <t>379220.147199053</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>373926.282300288</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>15.298</t>
+          <t>382331.873657504</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>18.288</t>
+          <t>403566.934130755</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>189570.321</t>
+          <t>235794.555800446</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>187155.714</t>
+          <t>239690.113256321</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>186671.186</t>
+          <t>244297.879288728</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>187705.421</t>
+          <t>282387.807893002</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>184930.821</t>
+          <t>333844.663389734</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>186868.916</t>
+          <t>382854.727645563</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>185021.452</t>
+          <t>422894.607307721</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>189025.774</t>
+          <t>539973.567329159</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>186711.658</t>
+          <t>621416.055405493</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>191182.623</t>
+          <t>649042.794429539</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>187841.283</t>
+          <t>809581.247022344</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>192533.713</t>
+          <t>925467.025260991</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>209722.628</t>
+          <t>912811.065013584</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>229190.16</t>
+          <t>937250.705962325</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>230929.681</t>
+          <t>990200.259261768</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>134.92</t>
+          <t>1259248.34376209</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>140.39</t>
+          <t>1314868.07418997</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>143.56</t>
+          <t>1377426.97855563</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>145.55</t>
+          <t>1610678.88373165</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>153.89</t>
+          <t>1926648.53401267</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>157.51</t>
+          <t>2209560.42545759</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>166.97</t>
+          <t>2482476.39621009</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>169.09</t>
+          <t>3170969.84644305</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>180.15</t>
+          <t>3532815.94243658</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>182.37</t>
+          <t>3603373.34265588</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>189.02</t>
+          <t>4412868.90443772</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>183.42</t>
+          <t>5074613.97489521</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>193.08</t>
+          <t>5346701.1591533</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>200.23</t>
+          <t>5700423.07142781</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>223.88</t>
+          <t>6166054.3035903</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>43.171</t>
+          <t>436739.493769464</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>43.216</t>
+          <t>451728.949454047</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>43.622</t>
+          <t>453557.899801074</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>38.979</t>
+          <t>484956.252043179</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>35.698</t>
+          <t>523197.898210166</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>30.736</t>
+          <t>557886.562577143</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>26.775</t>
+          <t>590013.72405179</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>21.153</t>
+          <t>642630.386624088</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>707894.38796839</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>18.999</t>
+          <t>765538.216745508</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>824103.153427702</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>13.725</t>
+          <t>879973.132166679</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>15.953</t>
+          <t>923003.093822051</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>17.152</t>
+          <t>975494.316212112</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>15.921</t>
+          <t>1042316.86568413</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>186688.311243224</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>190192.318907424</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>191730.641768615</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>195509.844548648</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>197943.396442642</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>216058.77448494</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>236926.292698209</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>261537.801141303</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>279448.554608388</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>301847.225844489</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>326995.930388364</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>363421.354012378</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>381929.801573414</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>402710.452611101</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>429656.570397707</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>221240.53546898</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>233553.128757001</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>249374.260478983</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>293859.904595118</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>337343.867894776</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>403279.55520604</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>468773.194534597</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>595350.814409595</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>631837.257932283</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>641500.833290105</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>808996.143093849</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>918491.270353167</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>910373.057028967</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>949022.857473917</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1004113.93122531</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>445332627000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>449907673000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>454652700000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>460906026000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>469523859000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>481211636000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>493947562000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>508653299000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>523074027000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>539838332000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>542896428000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>545686993000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>614660341000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>688095379000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>747929795000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>946052945525.205</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>973681830093.161</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1002443878447.26</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1033812502511.78</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1068802725066.67</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1077779934232.21</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1077119507853.15</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1078735396947.16</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1080383099414.01</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1084735105192.72</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1096986716367.36</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1116767368795.53</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1274604662813.14</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1438109826441.88</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1557808827706.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>759428979889.746</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>779128020914.484</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>800332100250.639</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>822943358524.539</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>846859139878.412</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>850129243775.652</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>846041956515.516</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>843646657380.445</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>843279449043.228</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>844792125997.793</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>849050543738.707</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>856546315280.055</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>971914662850.404</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1083944398822.84</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1155520750857.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>410063444</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>420902877</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>432113285</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>444312235</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>457919360</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>460240170</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>459570160</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>459864020</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>460178296</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>461620466</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>466169307</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>473774818</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>540263370</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>609186497</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>658776148</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>193583184</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>194761653</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>195963630</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>197755615</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>200488805</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>204577246</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>209874433</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>215986651</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>221964627</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>228908309</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>229699273</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>230251378</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>259217937</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>290083084</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>314881991</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>946052945525.205</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>973681830093.161</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1002443878447.26</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1033812502511.78</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1068802725066.67</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1077779934232.21</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1077119507853.15</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1078735396947.16</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1080383099414.01</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1084735105192.72</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1096986716367.36</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1116767368795.53</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1274604662813.14</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1438109826441.88</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1557808827706.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>445332627000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>449907673000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>454652700000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>460906026000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>469523859000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>481211636000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>493947562000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>508653299000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>523074027000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>539838332000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>542896428000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>545686993000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>614660341000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>688095379000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>747929795000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>889777.384223659</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>930507.62886154</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>983486.012994518</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1168335.43124015</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1382823.36808295</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1608557.12264892</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1853972.07381421</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2351594.12058147</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2588525.09056901</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2636498.48519716</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>3338037.48672886</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3865701.52427261</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>3720169.29890541</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3780995.42850508</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>3983527.12113965</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>457035.091692524</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>473243.243242603</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>493672.137855166</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>576247.711586149</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>671188.524530264</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>786134.282420629</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>891667.802372195</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1135324.37948551</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1253253.31063191</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1290543.6293736</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1618577.39840716</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1843958.28340608</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1823184.12204255</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1886273.55519253</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1994314.19233914</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2263412.60973955</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2407441.99831333</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2480662.26635869</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2663228.10473813</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2950533.51962918</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3147471.52473957</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3398933.37857223</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3706917.81104757</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3969238.87410836</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4207793.34816881</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>4492024.90118062</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>4866391.71872957</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>5488030.04272958</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>6060572.77169115</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>6652720.9801537</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
